--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129875269</v>
       </c>
       <c r="B2" t="n">
-        <v>98801</v>
+        <v>98811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129875269</v>
       </c>
       <c r="B2" t="n">
-        <v>98811</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129875268</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129875269</v>
       </c>
       <c r="B2" t="n">
-        <v>98815</v>
+        <v>98818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129875268</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129875269</v>
       </c>
       <c r="B2" t="n">
-        <v>98818</v>
+        <v>98819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129875268</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129875269</v>
       </c>
       <c r="B2" t="n">
-        <v>98819</v>
+        <v>98836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129875268</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129875269</v>
       </c>
       <c r="B2" t="n">
-        <v>98852</v>
+        <v>98854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129875269</v>
       </c>
       <c r="B2" t="n">
-        <v>98854</v>
+        <v>98941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129875268</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129875269</v>
+        <v>129875268</v>
       </c>
       <c r="B2" t="n">
-        <v>98854</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478274</v>
+        <v>478275</v>
       </c>
       <c r="R2" t="n">
-        <v>7030650</v>
+        <v>7030654</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,45 +776,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129875268</v>
+        <v>129875256</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>56884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Källmyren Aspås, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478275</v>
+        <v>478316</v>
       </c>
       <c r="R3" t="n">
-        <v>7030654</v>
+        <v>7030675</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +874,511 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129875253</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102463</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vägkant intill Källmyren Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478249</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7030528</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129875254</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102463</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vägkant intill Källmyren Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478218</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7030610</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129875255</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102463</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vägkant intill Källmyren Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478210</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7030656</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129875267</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Källmyren Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478266</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7030688</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129875269</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Källmyren Aspås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478274</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7030650</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>

--- a/artfynd/A 60487-2024 artfynd.xlsx
+++ b/artfynd/A 60487-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875268</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875256</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875253</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875254</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875255</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875267</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,8 +1418,22 @@
           <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129875269</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>